--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,7 +424,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -444,7 +444,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -653,6 +658,10 @@
   </si>
   <si>
     <t>FR Core Organization Description Extension</t>
+  </si>
+  <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3738,7 +3747,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3798,7 +3807,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3818,13 +3827,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3846,13 +3855,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3912,7 +3921,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3932,13 +3941,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3960,13 +3969,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4046,10 +4055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4075,16 +4084,16 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4133,7 +4142,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4162,10 +4171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4188,17 +4197,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4247,7 +4256,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4256,30 +4265,30 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4388,10 +4397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4502,10 +4511,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4531,16 +4540,16 @@
         <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4565,11 +4574,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4587,7 +4596,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4605,7 +4614,7 @@
         <v>191</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4616,10 +4625,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4642,19 +4651,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4683,7 +4692,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4701,7 +4710,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4716,10 +4725,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4739,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4759,16 +4768,16 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4781,7 +4790,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -4817,7 +4826,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4832,13 +4841,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4846,10 +4855,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4875,13 +4884,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4895,7 +4904,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -4931,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4946,13 +4955,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4960,10 +4969,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4986,13 +4995,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5043,7 +5052,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5058,13 +5067,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5072,10 +5081,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5098,16 +5107,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5157,7 +5166,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5172,13 +5181,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5186,10 +5195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5212,70 +5221,70 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="R32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5290,24 +5299,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5330,19 +5339,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5371,7 +5380,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5389,7 +5398,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5404,24 +5413,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5447,16 +5456,16 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5514,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5514,19 +5523,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5534,10 +5543,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5563,16 +5572,16 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5621,7 +5630,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5639,7 +5648,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5650,10 +5659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5676,19 +5685,19 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5737,7 +5746,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5746,19 +5755,19 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5766,10 +5775,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5792,19 +5801,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5853,7 +5862,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5862,19 +5871,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5882,10 +5891,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5908,17 +5917,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5967,7 +5976,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5982,10 +5991,10 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>106</v>
@@ -5996,10 +6005,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6108,10 +6117,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6222,10 +6231,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6251,13 +6260,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6307,7 +6316,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6316,7 +6325,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6336,10 +6345,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6365,13 +6374,13 @@
         <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6401,7 +6410,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6419,7 +6428,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6448,10 +6457,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6474,16 +6483,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6533,7 +6542,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6551,7 +6560,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6562,10 +6571,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6591,13 +6600,13 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6647,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6676,10 +6685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6702,19 +6711,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6763,7 +6772,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6781,7 +6790,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6792,10 +6801,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6904,10 +6913,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7018,14 +7027,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7047,16 +7056,16 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7105,7 +7114,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7134,10 +7143,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7160,17 +7169,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7198,10 +7207,10 @@
         <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7219,7 +7228,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7237,7 +7246,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7248,10 +7257,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7274,17 +7283,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7333,7 +7342,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7348,10 +7357,10 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7362,10 +7371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7388,17 +7397,17 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7447,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7462,10 +7471,10 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7476,10 +7485,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7502,17 +7511,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7561,7 +7570,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7576,10 +7585,10 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7590,10 +7599,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7616,17 +7625,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7675,7 +7684,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4035,7 +4035,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,10 +695,10 @@
     <t>closureReason</t>
   </si>
   <si>
-    <t>Organization.extension:members</t>
-  </si>
-  <si>
-    <t>members</t>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,14 +650,18 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description|0.1.0}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Additional details about the Organization that could be displayed as further information to identify the Organization beyond its name (new)</t>
+  </si>
+  <si>
+    <t>R5: `Organization.description` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `Organization.description` has a context of Organization based on following the parent source element upwards and mapping to `Organization`.
+Element `Organization.description` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3770,7 +3774,9 @@
       <c r="M20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3837,7 +3843,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3848,13 +3854,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3876,13 +3882,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3962,13 +3968,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -3990,16 +3996,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4078,13 +4084,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4106,16 +4112,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4194,13 +4200,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4222,13 +4228,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4308,13 +4314,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4336,13 +4342,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4422,13 +4428,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -4450,13 +4456,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4536,10 +4542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4565,16 +4571,16 @@
         <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4623,7 +4629,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4652,10 +4658,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4678,17 +4684,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4737,7 +4743,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4746,30 +4752,30 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4792,70 +4798,70 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="R29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="R29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4870,24 +4876,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4910,26 +4916,26 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -4951,7 +4957,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -4969,7 +4975,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4984,24 +4990,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5027,16 +5033,16 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5085,7 +5091,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5094,19 +5100,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5114,10 +5120,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5143,16 +5149,16 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5201,7 +5207,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5219,7 +5225,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5230,10 +5236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5256,19 +5262,19 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5317,7 +5323,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5326,19 +5332,19 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5352,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5372,19 +5378,19 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5433,7 +5439,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5442,19 +5448,19 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5462,10 +5468,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5488,17 +5494,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5547,7 +5553,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5562,10 +5568,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>106</v>
@@ -5576,10 +5582,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5688,10 +5694,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5802,10 +5808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5831,13 +5837,13 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5887,7 +5893,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5896,7 +5902,7 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
@@ -5916,10 +5922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5945,13 +5951,13 @@
         <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5981,7 +5987,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -5999,7 +6005,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6028,10 +6034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6054,16 +6060,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6113,7 +6119,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6131,7 +6137,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6142,10 +6148,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6171,13 +6177,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6227,7 +6233,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6256,10 +6262,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6282,19 +6288,19 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6343,7 +6349,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6361,7 +6367,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6372,10 +6378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6484,10 +6490,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6598,14 +6604,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6627,16 +6633,16 @@
         <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6685,7 +6691,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6714,10 +6720,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6740,17 +6746,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6778,10 +6784,10 @@
         <v>150</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6799,7 +6805,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6817,7 +6823,7 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6828,10 +6834,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6854,17 +6860,17 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -6913,7 +6919,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6928,10 +6934,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -6942,10 +6948,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6968,17 +6974,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7027,7 +7033,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7042,10 +7048,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7056,10 +7062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7082,17 +7088,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7141,7 +7147,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7156,10 +7162,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7170,10 +7176,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7196,17 +7202,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7255,7 +7261,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -770,7 +770,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organization business identifier</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -874,7 +874,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
+    <t>Name of the organization</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
@@ -918,7 +918,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
+    <t>Organization telecom</t>
   </si>
   <si>
     <t>A contact detail for the organization.</t>
@@ -990,7 +990,7 @@
 </t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>The organization of which this organization is part of: e.g. an ERN</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1086,7 +1086,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
+    <t>Organization contact infos</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
